--- a/CardArchive/Tools/DataExport/Pack.xlsx
+++ b/CardArchive/Tools/DataExport/Pack.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="References" sheetId="1" r:id="rId1"/>
-    <sheet name="Enums" sheetId="2" r:id="rId2"/>
-    <sheet name="Pack" sheetId="3" r:id="rId3"/>
+    <sheet name="Reference" sheetId="1" r:id="rId1"/>
+    <sheet name="Enum" sheetId="2" r:id="rId2"/>
+    <sheet name="_컬럼 설명" sheetId="3" r:id="rId3"/>
+    <sheet name="Pack" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -13,42 +14,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">File</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">!EndTable</t>
-        </is>
-      </c>
+      <c r="A1"/>
+      <c r="B1"/>
+      <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">string</t>
+      <c r="A2"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Reference</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rarity.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rarity.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A3"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Reference</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">Variant.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">!EndTable</t>
         </is>
       </c>
     </row>
@@ -59,44 +51,81 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_PackType</t>
-        </is>
-      </c>
-      <c r="B1"/>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">!EndTable</t>
-        </is>
-      </c>
-    </row>
+    <row r="1"/>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2"/>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enum</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PackType</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!GenerateCsEnum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">Random</t>
         </is>
       </c>
-      <c r="B2">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PackType</t>
+        </is>
+      </c>
+      <c r="G3">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="4">
+      <c r="A4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">Fixed</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PackType</t>
+        </is>
+      </c>
+      <c r="G4">
         <v>10</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">!EndTable</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -106,265 +135,623 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="A2"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TableName</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">설명</t>
+        </is>
+      </c>
+      <c r="C3"/>
+    </row>
+    <row r="4">
+      <c r="A4"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Detail</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">설명</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!EndField</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5"/>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Id</t>
+        </is>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+    </row>
+    <row r="6">
+      <c r="A6"/>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">available</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+    </row>
+    <row r="7">
+      <c r="A7"/>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cardback_img</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
+    </row>
+    <row r="8">
+      <c r="A8"/>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cards</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+    </row>
+    <row r="9">
+      <c r="A9"/>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cost</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
+    </row>
+    <row r="10">
+      <c r="A10"/>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desc</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+    </row>
+    <row r="11">
+      <c r="A11"/>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pack_img</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+    </row>
+    <row r="12">
+      <c r="A12"/>
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rarities</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PackRarity[]</t>
+        </is>
+      </c>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+    </row>
+    <row r="13">
+      <c r="A13"/>
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rarities_1st</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PackRarity[]</t>
+        </is>
+      </c>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+    </row>
+    <row r="14">
+      <c r="A14"/>
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sort_order</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+    </row>
+    <row r="15">
+      <c r="A15"/>
+      <c r="B15">
+        <v>11</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">title</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+    </row>
+    <row r="16">
+      <c r="A16"/>
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PackType</t>
+        </is>
+      </c>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+    </row>
+    <row r="17">
+      <c r="A17"/>
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variants</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PackVariant[]</t>
+        </is>
+      </c>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
+    </row>
+    <row r="18">
+      <c r="A18"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!EndTable</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1"/>
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Table</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pack</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!AutoKey;!GenerateCsEnum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2"/>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">available</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">cardback_img</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">cards</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">cost</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">desc</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve">pack_img</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">rarities</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">rarities_1st</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">sort_order</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t xml:space="preserve">title</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t xml:space="preserve">type</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t xml:space="preserve">variants</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">!EndTable</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_Pack</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bool</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">path</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">int</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">int</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">string</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">path</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!EndField</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Id</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">PackRarity[]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">PackRarity[]</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">int</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">string</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_PackType</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PackType</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t xml:space="preserve">PackVariant[]</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="4">
+      <c r="A4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">elite</t>
         </is>
       </c>
-      <c r="B3" t="b">
+      <c r="E4">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">Assets/TcgEngine/Sprites/Cardbacks/cardback_gold.png</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="G4">
         <v>5</v>
       </c>
-      <c r="E3">
+      <c r="H4">
         <v>250</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">Elite pack with 5 cards. More chance to find rares and mythics.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve">Assets/TcgEngine/Sprites/Cardbacks/pack_gold.png</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">rarity=common,probability=80;rarity=uncommon,probability=12;rarity=rare,probability=6;rarity=mythic,probability=2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">rarity=rare,probability=70;rarity=mythic,probability=30</t>
         </is>
       </c>
-      <c r="J3">
+      <c r="M4">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">Elite Pack</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t xml:space="preserve">Random</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t xml:space="preserve">variant=normal,probability=90;variant=foil,probability=10</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5"/>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">standard</t>
         </is>
       </c>
-      <c r="B4" t="b">
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t xml:space="preserve">Assets/TcgEngine/Sprites/Cardbacks/cardback_silver.png</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="G5">
         <v>5</v>
       </c>
-      <c r="E4">
+      <c r="H5">
         <v>100</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">Standard pack with 5 cards.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve">Assets/TcgEngine/Sprites/Cardbacks/pack_silver.png</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">rarity=common,probability=80;rarity=uncommon,probability=12;rarity=rare,probability=6;rarity=mythic,probability=2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">rarity=uncommon,probability=60;rarity=rare,probability=30;rarity=mythic,probability=10</t>
         </is>
       </c>
-      <c r="J4">
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t xml:space="preserve">Standard Pack</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t xml:space="preserve">Random</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t xml:space="preserve">variant=normal,probability=96;variant=foil,probability=4</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">!EndTable</t>
         </is>

--- a/CardArchive/Tools/DataExport/Pack.xlsx
+++ b/CardArchive/Tools/DataExport/Pack.xlsx
@@ -8,6 +8,44 @@
     <sheet name="Pack" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
+    <font/>
+    <font>
+      <b/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border/>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+</styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -160,37 +198,37 @@
     </row>
     <row r="4">
       <c r="A4"/>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Name</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Type</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Detail</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">설명</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">비고</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">!EndField</t>
         </is>
